--- a/data/trans_dic/P55$familiarvive-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,96</t>
+          <t>0,0; 58,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 40,09</t>
+          <t>3,97; 38,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,98</t>
+          <t>0,0; 47,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,32</t>
+          <t>0,0; 68,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 43,18</t>
+          <t>7,91; 39,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,52</t>
+          <t>0,0; 32,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,54</t>
+          <t>0,0; 50,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,48</t>
+          <t>0,0; 33,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 32,0</t>
+          <t>8,96; 31,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,27</t>
+          <t>0,0; 54,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,07</t>
+          <t>0,0; 55,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,57</t>
+          <t>0,0; 50,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,0</t>
+          <t>0,0; 27,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,82</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,0</t>
+          <t>0,0; 62,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 27,61</t>
+          <t>2,83; 27,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 51,08</t>
+          <t>5,78; 53,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 46,37</t>
+          <t>5,32; 44,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,19</t>
+          <t>0,0; 33,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 21,56</t>
+          <t>3,71; 22,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,81</t>
+          <t>0,0; 30,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,69</t>
+          <t>3,7; 32,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,0; 54,55</t>
+          <t>13,69; 56,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 37,27</t>
+          <t>9,59; 38,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,9</t>
+          <t>0,0; 69,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 37,89</t>
+          <t>5,19; 38,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 60,9</t>
+          <t>7,18; 57,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 27,62</t>
+          <t>4,47; 26,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 34,63</t>
+          <t>4,27; 34,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 28,01</t>
+          <t>4,75; 28,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,65; 47,87</t>
+          <t>15,1; 48,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 26,35</t>
+          <t>9,44; 27,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 28,51</t>
+          <t>10,77; 28,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,91; 37,78</t>
+          <t>12,9; 35,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 28,99</t>
+          <t>6,46; 27,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 16,38</t>
+          <t>4,6; 16,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 52,55</t>
+          <t>10,64; 50,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 42,36</t>
+          <t>4,85; 42,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 41,32</t>
+          <t>8,03; 42,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 31,12</t>
+          <t>12,65; 30,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 30,4</t>
+          <t>14,06; 30,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,28; 32,93</t>
+          <t>14,23; 33,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 27,68</t>
+          <t>9,99; 30,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 18,73</t>
+          <t>8,96; 18,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 40,75</t>
+          <t>5,19; 41,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 30,89</t>
+          <t>6,05; 28,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 22,19</t>
+          <t>4,15; 21,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 19,87</t>
+          <t>3,28; 20,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 38,44</t>
+          <t>7,56; 39,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,42; 43,3</t>
+          <t>22,5; 44,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 43,99</t>
+          <t>15,21; 43,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 25,18</t>
+          <t>13,33; 24,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,92; 31,93</t>
+          <t>8,99; 31,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 36,59</t>
+          <t>19,92; 36,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 30,25</t>
+          <t>12,65; 29,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 20,92</t>
+          <t>12,48; 21,67</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,2; 42,44</t>
+          <t>26,82; 42,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,88; 39,26</t>
+          <t>22,51; 38,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,1; 36,05</t>
+          <t>19,65; 35,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,68; 28,25</t>
+          <t>17,65; 28,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,59; 42,45</t>
+          <t>26,6; 42,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,88; 39,26</t>
+          <t>22,51; 38,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,1; 36,05</t>
+          <t>19,65; 35,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,44; 28,1</t>
+          <t>17,78; 27,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 22,41</t>
+          <t>9,94; 22,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 26,09</t>
+          <t>11,84; 25,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,44; 21,32</t>
+          <t>9,96; 22,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 15,27</t>
+          <t>7,48; 15,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,77; 37,24</t>
+          <t>24,37; 37,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,75; 35,44</t>
+          <t>23,49; 34,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,2; 31,96</t>
+          <t>19,66; 32,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 23,5</t>
+          <t>16,85; 23,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,76; 29,66</t>
+          <t>20,75; 30,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,23; 29,86</t>
+          <t>21,36; 30,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,31; 27,3</t>
+          <t>18,28; 27,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,97; 19,85</t>
+          <t>14,71; 19,86</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4868</t>
+          <t>0; 4873</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>442; 4809</t>
+          <t>477; 4668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5879</t>
+          <t>0; 6362</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1082; 5984</t>
+          <t>1096; 5420</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6705</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5777</t>
+          <t>0; 5833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 4990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2219; 8273</t>
+          <t>2315; 8260</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5860</t>
+          <t>0; 5882</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5047</t>
+          <t>0; 5230</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 5412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4714</t>
+          <t>0; 4761</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 5352</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5549</t>
+          <t>0; 5537</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1773</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>389; 3788</t>
+          <t>388; 3779</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>981; 8249</t>
+          <t>934; 8613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>974; 8493</t>
+          <t>974; 8143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5971</t>
+          <t>0; 5804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1098; 6721</t>
+          <t>1155; 6934</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5192</t>
+          <t>0; 5434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>905; 7744</t>
+          <t>903; 7838</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2143; 8992</t>
+          <t>2256; 9268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2014; 7897</t>
+          <t>2031; 8119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5650</t>
+          <t>0; 5811</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>977; 7199</t>
+          <t>986; 7269</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1264; 9927</t>
+          <t>1170; 9322</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1287; 5850</t>
+          <t>947; 5662</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1128; 9121</t>
+          <t>1124; 9093</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2175; 12165</t>
+          <t>2064; 12455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5460; 15693</t>
+          <t>4951; 15942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4004; 11163</t>
+          <t>4001; 11798</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7706; 20137</t>
+          <t>7609; 20048</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9427; 25611</t>
+          <t>8742; 24272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2733; 11558</t>
+          <t>2576; 10816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3272; 11802</t>
+          <t>3313; 11761</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3300; 12307</t>
+          <t>2492; 11823</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>956; 8827</t>
+          <t>1011; 8946</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2600; 13564</t>
+          <t>2637; 13833</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5340; 12069</t>
+          <t>4907; 11981</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13530; 28591</t>
+          <t>13220; 28791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12653; 29186</t>
+          <t>12611; 29846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6951; 20118</t>
+          <t>7259; 22289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10095; 20755</t>
+          <t>9930; 20822</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>829; 6551</t>
+          <t>834; 6662</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2214; 11129</t>
+          <t>2181; 10234</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1792; 10502</t>
+          <t>1965; 10250</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1112; 5975</t>
+          <t>987; 6055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2660; 13997</t>
+          <t>2754; 14207</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18737; 36181</t>
+          <t>18799; 37048</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8721; 23323</t>
+          <t>8065; 23154</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12918; 23472</t>
+          <t>12420; 22753</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5210; 16763</t>
+          <t>4720; 16597</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22943; 43753</t>
+          <t>23825; 43260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13068; 30354</t>
+          <t>12693; 29718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14705; 25786</t>
+          <t>15389; 26708</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37736; 61129</t>
+          <t>38631; 61465</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32740; 56183</t>
+          <t>32207; 55658</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29596; 53092</t>
+          <t>28940; 52707</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24934; 39826</t>
+          <t>24885; 39785</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38546; 61541</t>
+          <t>38563; 61478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32740; 56183</t>
+          <t>32207; 55658</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29596; 53092</t>
+          <t>28940; 52707</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24971; 40226</t>
+          <t>25457; 39797</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12488; 28367</t>
+          <t>12583; 28630</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17908; 38132</t>
+          <t>17303; 37958</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11466; 25897</t>
+          <t>12101; 26920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11135; 23644</t>
+          <t>11593; 23802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>57205; 85990</t>
+          <t>56279; 85605</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66145; 98715</t>
+          <t>65423; 97156</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53368; 84426</t>
+          <t>51945; 84808</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>54817; 75595</t>
+          <t>54215; 74554</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74219; 106044</t>
+          <t>74176; 108128</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90168; 126812</t>
+          <t>90740; 127574</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70621; 105279</t>
+          <t>70510; 104794</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>71331; 94607</t>
+          <t>70110; 94660</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiarvive-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,01</t>
+          <t>0,0; 57,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 38,91</t>
+          <t>3,56; 37,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,59</t>
+          <t>0,0; 47,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,4</t>
+          <t>0,0; 68,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,91; 39,11</t>
+          <t>7,21; 39,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,11</t>
+          <t>0,0; 31,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,02</t>
+          <t>0,0; 50,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,11</t>
+          <t>0,0; 40,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 31,95</t>
+          <t>7,26; 29,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -862,27 +862,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,0</t>
+          <t>0,0; 53,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,32</t>
+          <t>0,0; 46,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,28</t>
+          <t>0,0; 25,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 82,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,86</t>
+          <t>0,0; 62,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 27,55</t>
+          <t>2,73; 29,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 53,33</t>
+          <t>6,0; 54,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 44,45</t>
+          <t>0,0; 40,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,23</t>
+          <t>0,0; 32,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 22,24</t>
+          <t>3,19; 20,59</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,16</t>
+          <t>0,0; 29,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 32,08</t>
+          <t>4,06; 33,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 56,23</t>
+          <t>12,5; 55,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 38,32</t>
+          <t>9,43; 38,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,84</t>
+          <t>0,0; 66,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 38,26</t>
+          <t>5,13; 37,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 57,19</t>
+          <t>7,93; 59,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 26,73</t>
+          <t>5,05; 25,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 34,53</t>
+          <t>4,14; 33,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 28,67</t>
+          <t>6,49; 29,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 48,63</t>
+          <t>15,86; 48,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 27,85</t>
+          <t>9,94; 27,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 28,39</t>
+          <t>10,59; 29,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 35,8</t>
+          <t>13,82; 37,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 27,13</t>
+          <t>6,99; 29,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 16,33</t>
+          <t>4,0; 15,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 50,48</t>
+          <t>10,29; 51,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 42,93</t>
+          <t>4,83; 42,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 42,14</t>
+          <t>7,67; 41,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 30,89</t>
+          <t>13,1; 30,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 30,61</t>
+          <t>13,25; 29,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 33,68</t>
+          <t>13,43; 33,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 30,66</t>
+          <t>9,98; 27,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 18,79</t>
+          <t>8,41; 18,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 41,43</t>
+          <t>5,15; 41,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 28,4</t>
+          <t>6,2; 30,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 21,66</t>
+          <t>3,8; 21,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 20,14</t>
+          <t>4,01; 20,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 39,02</t>
+          <t>9,68; 38,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,5; 44,34</t>
+          <t>22,06; 43,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,21; 43,67</t>
+          <t>16,15; 43,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,33; 24,41</t>
+          <t>13,73; 25,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 31,62</t>
+          <t>10,19; 32,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,92; 36,17</t>
+          <t>19,63; 36,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,65; 29,61</t>
+          <t>12,04; 30,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,48; 21,67</t>
+          <t>12,66; 21,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,82; 42,67</t>
+          <t>25,84; 43,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 38,9</t>
+          <t>23,11; 38,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 35,79</t>
+          <t>20,15; 37,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,65; 28,22</t>
+          <t>18,02; 28,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,6; 42,41</t>
+          <t>26,3; 42,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 38,9</t>
+          <t>23,11; 38,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 35,79</t>
+          <t>20,15; 37,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,78; 27,8</t>
+          <t>17,68; 27,71</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,94; 22,62</t>
+          <t>9,86; 22,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 25,97</t>
+          <t>12,08; 26,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 22,16</t>
+          <t>9,5; 21,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 15,37</t>
+          <t>7,43; 15,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,37; 37,07</t>
+          <t>24,39; 36,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,49; 34,88</t>
+          <t>23,99; 34,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,66; 32,1</t>
+          <t>20,72; 32,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,85; 23,17</t>
+          <t>17,29; 23,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,75; 30,25</t>
+          <t>20,76; 30,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,36; 30,04</t>
+          <t>21,2; 29,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,28; 27,18</t>
+          <t>18,21; 27,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,71; 19,86</t>
+          <t>14,91; 19,96</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4702</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4873</t>
+          <t>0; 4836</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>477; 4668</t>
+          <t>445; 4625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6362</t>
+          <t>0; 6329</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5503</t>
+          <t>0; 5480</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1096; 5420</t>
+          <t>1081; 5859</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7549</t>
+          <t>0; 7343</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5833</t>
+          <t>0; 5849</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 6161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2315; 8260</t>
+          <t>1996; 8240</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3254</t>
         </is>
       </c>
     </row>
@@ -2140,27 +2140,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5230</t>
+          <t>0; 5047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5412</t>
+          <t>0; 4977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4761</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5352</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5537</t>
+          <t>0; 5510</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>388; 3779</t>
+          <t>424; 4648</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>934; 8613</t>
+          <t>969; 8823</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>974; 8143</t>
+          <t>0; 7421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5804</t>
+          <t>0; 5674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1155; 6934</t>
+          <t>1095; 7061</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>8152</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5434</t>
+          <t>0; 5305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>903; 7838</t>
+          <t>991; 8203</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2256; 9268</t>
+          <t>2060; 9206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2031; 8119</t>
+          <t>2149; 8671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5811</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>986; 7269</t>
+          <t>975; 7163</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1170; 9322</t>
+          <t>1293; 9757</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>947; 5662</t>
+          <t>1206; 6111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1124; 9093</t>
+          <t>1091; 8882</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2064; 12455</t>
+          <t>2821; 12631</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4951; 15942</t>
+          <t>5200; 15832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4001; 11798</t>
+          <t>4637; 12818</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>15491</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7609; 20048</t>
+          <t>7480; 20681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8742; 24272</t>
+          <t>9368; 25323</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2576; 10816</t>
+          <t>2786; 11848</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3313; 11761</t>
+          <t>3083; 12209</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2492; 11823</t>
+          <t>2411; 12020</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1011; 8946</t>
+          <t>1006; 8938</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2637; 13833</t>
+          <t>2519; 13771</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4907; 11981</t>
+          <t>5480; 12933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13220; 28791</t>
+          <t>12466; 27736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12611; 29846</t>
+          <t>11899; 29534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7259; 22289</t>
+          <t>7252; 20240</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9930; 20822</t>
+          <t>10001; 21697</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>22746</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>834; 6662</t>
+          <t>829; 6592</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2181; 10234</t>
+          <t>2232; 10998</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1965; 10250</t>
+          <t>1799; 10289</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>987; 6055</t>
+          <t>1319; 6687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2754; 14207</t>
+          <t>3524; 14050</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18799; 37048</t>
+          <t>18429; 36442</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8065; 23154</t>
+          <t>8563; 23178</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12420; 22753</t>
+          <t>13828; 25675</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4720; 16597</t>
+          <t>5350; 17025</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23825; 43260</t>
+          <t>23473; 44107</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12693; 29718</t>
+          <t>12078; 30338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15389; 26708</t>
+          <t>16910; 29356</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>34779</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38631; 61465</t>
+          <t>37229; 62032</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32207; 55658</t>
+          <t>33065; 55690</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28940; 52707</t>
+          <t>29678; 54652</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24885; 39785</t>
+          <t>27407; 43580</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38563; 61478</t>
+          <t>38123; 61446</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32207; 55658</t>
+          <t>33065; 55690</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28940; 52707</t>
+          <t>29678; 54652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25457; 39797</t>
+          <t>27285; 42750</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>64962</t>
+          <t>70641</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81941</t>
+          <t>89125</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12583; 28630</t>
+          <t>12479; 28676</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17303; 37958</t>
+          <t>17651; 38661</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12101; 26920</t>
+          <t>11535; 26314</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11593; 23802</t>
+          <t>12356; 25424</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>56279; 85605</t>
+          <t>56317; 84259</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65423; 97156</t>
+          <t>66820; 96698</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51945; 84808</t>
+          <t>54741; 86622</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>54215; 74554</t>
+          <t>60337; 82353</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74176; 108128</t>
+          <t>74223; 108590</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90740; 127574</t>
+          <t>90027; 125833</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70510; 104794</t>
+          <t>70230; 105478</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>70110; 94660</t>
+          <t>76825; 102862</t>
         </is>
       </c>
     </row>
